--- a/pet_needs_pipeline/outputs/tables/ig_cluster_hypo.xlsx
+++ b/pet_needs_pipeline/outputs/tables/ig_cluster_hypo.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,33 +445,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>321</v>
+        <v>877</v>
       </c>
       <c r="C2" t="n">
-        <v>321</v>
+        <v>866</v>
       </c>
       <c r="D2" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>556</v>
-      </c>
-      <c r="C3" t="n">
-        <v>545</v>
-      </c>
-      <c r="D3" t="n">
-        <v>472</v>
+        <v>777</v>
       </c>
     </row>
   </sheetData>
@@ -485,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,206 +497,104 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0189</v>
+        <v>0.0232</v>
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0154</v>
+        <v>0.0284</v>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>0.017</v>
+        <v>0.0303</v>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.016</v>
+        <v>0.0316</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0197</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+        <v>0.0377</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0193</v>
+        <v>0.0385</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0176</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0449</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.0541</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.0578</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.0555</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.0641</v>
-      </c>
-      <c r="D14" t="inlineStr">
+        <v>0.0397</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.0598</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -725,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,37 +700,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="D2" t="n">
-        <v>25.2</v>
+        <v>47.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>끄다, 모음, 모르다, 걸리다, 언니, 소금, 미용실, 보고, 게임, 다녀오다</t>
+          <t>알다, 사진, 아니다, 가다, 사용, 보고, 먹다, 간식, 해보다, 모습</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -860,47 +742,47 @@
         <v>0.04</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="D3" t="n">
-        <v>18.7</v>
+        <v>10.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>어디, 보안, 사용, 혼자, 기능, 반려동물, 확인, 해주다, 일상, 걱정</t>
+          <t>좋다, 넘다, 화질, 소식, 보이다, 바라다, 가득하다, 자동, 바꾸다, 응원</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -912,286 +794,278 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="O3" t="n">
-        <v>0.37</v>
+        <v>0.06</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>H3 불안·죄책감(30%) / H5 사각지대·고정형(26%) / R1 보안·프라이버시(40%) / S1 돌봄공백(37%)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="D4" t="n">
-        <v>13.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>간식, 아니다, 기다리다, 주인, 외출, 주다, 혼자, 소개, 언니, 이제</t>
+          <t>자다, 혼자, 모습, 귀엽다, 서도, 얌전하다, 쳐다보다, 마루, 놀다, 이쁘다</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="G4" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="O4" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>S1 돌봄공백(43%)</t>
+          <t>S1 돌봄공백(25%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="D5" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>자다, 혼자, 저기, 출근, 놀다, 넘다, 서도, 엄마, 일어나다, 밉다</t>
+          <t>귀엽다, 넘다, 마루, 아니다, 망콩, 찾다, 끄다, 눕다, 대견하다, 꼬미</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>0.04</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>S1 돌봄공백(44%)</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D6" t="n">
-        <v>8.9</v>
+        <v>6.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>분리, 불안, 생기다, 소리, 자다, 엄마, 혼자, 짖다, 나가다, 설치</t>
+          <t>혼자, 사랑, 이제, 연습, 두발, 오빠, 받다, 국내, 기쁨, 반려동물</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.67</v>
+        <v>0.17</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.19</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.04</v>
-      </c>
       <c r="O6" t="n">
-        <v>0.33</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>H2 문제행동(67%) / H3 불안·죄책감(67%) / S1 돌봄공백(33%)</t>
+          <t>S1 돌봄공백(56%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>8.5</v>
+        <v>5.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>귀엽다, 움직이다, 자다, 캡쳐, 쳐다보다, 눕다, 화질, 좋다, 다니다, 볼때</t>
+          <t>구름, 친구, 놀다, 하자, 귀요미, 안뇽, 자주, 사랑스럽다, 안녕, 생일</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.15</v>
+        <v>0.02</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.04</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.08</v>
-      </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>알다, 훔치다, 마주치다, 보기, 쳐다보다, 아이컨택, 오빠, 강쥐, 자다, 모음</t>
+          <t>엄마, 가다, 혼자, 지켜보다, 불다, 출근, 아빠, 대다, 자다, 동안</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G8" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1203,54 +1077,50 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N8" t="n">
-        <v>0.32</v>
+        <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="P8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>R1 보안·프라이버시(32%)</t>
-        </is>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>7.9</v>
+        <v>3.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>가다, 먹다, 쳐다보다, 사다, 엄마, 동안, 이상하다, 항상, 꼬리, 서다</t>
+          <t>분리, 불안, 생기다, 부럽다, 주인, 혼자, 설치, 자다, 티비, 은동</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="G9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.08</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.04</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1265,47 +1135,51 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="P9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>H2 문제행동(88%) / H3 불안·죄책감(96%)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>댓글</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>55.3</v>
+        <v>2.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>넘다, 사진, 엄마, 알다, 백설, 최고, 되어다, 완료, 먹다, 해주다</t>
+          <t>백설, 표정, 뭔가, 언니, 예쁘다, 모르다, 토리, 대박, 쳐다보다, 자연</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1317,37 +1191,37 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>댓글</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>12.1</v>
+        <v>2.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>좋다, 화질, 응원, 소식, 가득하다, 정답, 바라다, 보이다, 넘다, 자동</t>
+          <t>대란, 살다, 로봇, 든든하다, 일상, 행복, 친구, 휴식, 편안하다, 사랑</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1360,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1372,415 +1246,18 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C12" t="n">
-        <v>47</v>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>귀엽다, 찾다, 넘다, 마루, 아니다, 토리, 대견하다, 얼굴, 망콩, 가루</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>27</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>자다, 얌전하다, 모습, 귀엽다, 좋다, 마루, 귀요미, 호빵, 자고, 예쁘다</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" t="n">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>친구, 하자, 안뇽, 구름, 안녕, 사랑스럽다, 귀엽다, 이쁘다, 귀요미, 맞팔</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="n">
-        <v>17</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>살다, 로봇, 대란, 든든하다, 일상, 행복, 친구, 조금, 시작, 안전하다</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>16</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>분리, 불안, 부럽다, 불안도, 생기다, 댕댕, 티비, 설치, 쏘다, 똑같다</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>H2 문제행동(81%) / H3 불안·죄책감(94%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>7</v>
-      </c>
-      <c r="C17" t="n">
-        <v>16</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>혼자, 서도, 자다, 이쁘다, 배다, 흑임자, 후기, 삼치, 순간, 모습</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>S1 돌봄공백(100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>11</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>사랑, 두발, 이제, 오빠, 연습, 걷다, 혼자, 엄마, 아프다, 얼마나</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>S1 돌봄공백(27%)</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1793,7 +1270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1809,20 +1286,30 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>feed_type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>url</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>emotions</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>본문</t>
         </is>
@@ -1831,7 +1318,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1839,21 +1326,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C2REC47LhPN/</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>반려동물 천만시대! 기다리고 기다리던 그 카메라 그냥 홈 CCTV 카메라가 아니죠! 주인이 외출하면 혼자 쓸쓸하게 있을 반려동물.. 놀이처럼 원격으로 간식도 주고 학습도 되는 국내유일! 애완동물 간식기+홈 CCTV 로보뷰 펫 지금 바로 소개합니다~  ✅로보뷰공식몰    ✅ 유튜브채널    #애완동물 #강아지 #고양이 #펫캠 #펫카메라 #반려동물 #강아지카메라 #강아지간식기 #애견급식기 #사료급식기 #애완동물간식 #강아지간식 #강아지놀아주기 #강아지용품 #강아지용품추천 #로보뷰펫 #강아지cctv #cctv추천 #CCTV #홈카메라 #IP카메라 #홈캠 #보안카메라 #로보뷰</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DN7sPVlEkzY/#c17886474678222493</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>엄마 목소리가 들려서!!❤️❤️엄마 최고야😍</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1861,29 +1358,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C2Yz_GBrPPf/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>post</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>걱정</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>반려동물 천만시대!  외출하더라도 혼자있을 강아지, 고양이  이제부터 걱정마세요! 놀이처럼 원격으로 간식도 주고 학습도 되는 국내유일! 애완동물 간식기+홈 CCTV 로보뷰 펫 설치도 아주 간편해요  ✅로보뷰공식몰    ✅ 유튜브채널    #애완동물 #강아지 #고양이 #펫캠 #펫카메라 #반려동물 #강아지카메라 #강아지간식기 #애견급식기 #사료급식기 #애완동물간식 #강아지간식 #강아지놀아주기 #강아지용품 #강아지용품추천 #로보뷰펫 #강아지cctv #cctv추천 #CCTV #홈카메라 #IP카메라 #홈캠 #보안카메라 #로보뷰</t>
+          <t>https://www.instagram.com/p/DX8kHLnk09Z/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>🩵엄마 출근할동안 혼자 잘 놀아유 🩵 #강아지홈캠 #엄마가지켜보고있다😎</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1891,29 +1390,31 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Cy4mFcTP5c4/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>미안</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>📷카메라 낯가림 끝남 - 펫카메라 한 달 째~ 이브 공복시간을 줄이려고 큰 맘 먹고 구입. 화질도 좋고 간식도 줄 수 있어서 좋은데 앱이 너무 구림😤 한번에 연결되는 일이 없고 항상 두세번 로딩해야 들어가진다. 싼 카메라도 아닌데 이게 뭐람?  이브는 카메라로 말 걸 때마다 깜짝 놀라서 도망가더니 이제는 카메라로 부르면 쪼르르 카메라 앞으로 달려가고  급기야는 간식내놓으라고 괴롭힘ㅋㅋㅋ  매일 회사에서 지켜보는 재미가 있다ㅋㅋ 근데 카메라 돌리면 일어나서 쳐다봄... 미안행....조용히 보기만 할게🫠  나는야 이브 스토커~  #유피 #펫카메라</t>
+          <t>https://www.instagram.com/p/DXHWdX1AWDc/#c18091147556335548</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>엄마가 날 지켜보고 있다고 생각하게찌만.. 내가 지켜보고 이땨 👀</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1921,29 +1422,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DMr208wpn0V/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>걱정|불안</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>​👀 요즘 홈캠 고민하고 계신가요?​ 아이를 돌보는 맞벌이 가정, 혼자 계신 부모님, 혹은 집을 지키는 반려동물이 걱정되시나요?​ 언제 어디서든 집 안 상황을 확인할 수 있는 홈캠이 필수인 시대입니다.​  하지만 요즘 뉴스에 나오는 백도어 이슈, 보안 취약점…​ 타인의 눈에 내 일상이 노출될 수 있다는 불안감 때문에 고민이신가요?​  📌 “믿고 쓸 수 있는 홈캠 어디 없을까?”​ 보안을 최우선으로 생각한다면, 이글루 홈캠이 답입니다.​  ​🔒 국내 기술 + 국내 서버 = 믿을 수 있는 보안​ 📱 언제 어디서나 우리 반려동물/어르신 실시간 확인​  ​▶제품 상세정보 보기 :​</t>
+          <t>https://www.instagram.com/p/DZFJ7v9EkmK/#c18114296077655400</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>윤서도 코비처럼 잘 잤으면 🥲</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1951,29 +1454,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C7nrEiRpAZO/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>post</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>걱정|안심</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>이 포스팅은 BESPOKE AI 스팀 소개 목적으로 삼성전자로부터 제품을 지원 받아 작성되었습니다.  가끔씩 반려견 시루를 집에 혼자 두고 외출할 일이 있는데, 혼자서 잘 지내는 건가 궁금하기도 하고, 걱정도 되고 하거든요?! 그런데 비스포크 AI 스팀 로봇청소기는 펫 케어 기능이 있지 뭐예요?!!!   외출을 가정하고, 스마트싱스 앱에서, 우리 집 모니터링 – 반려동물 찾기를 하면 실시간으로 비스포크 AI 스팀에 장착된 카메라로 반려견을 찾아줍니다.  너무 신기했어요! ㅎㅎㅎ 집안 곳곳을 돌아다니면서 반려견을 탐지하고 찾으면 알림 메시지도 보내준답니다. (고양이도 인식할 수 있대요!) 짖음을 감지해서 짖음 횟수도 기록해 주네요! 그리고 혼자 있는 반려견을 위해서 정서적으로 안정되고 심심하지 않게 음악과 영</t>
+          <t>https://www.instagram.com/p/DW1s5OjGOg-/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>홈캠 속 구름이 … 잔다 … 계속 잔다 …</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1981,29 +1486,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DIgGRZ-TAO4/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>post</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>안심</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#제품제공   아이키우는집 , 그리고 반려동물을 키우는집에 필수로 있는 홈캠 ! 저는 아이오트 홈카메라 pro 를 선택했어요.  요 귀여운 홈 카메라 친구는 베이비캠, 펫캠, 홈캠으로 최고더라구요.  저희집은 또 애만 있는 집이 아니라 애개육아를 함께 하고있는 집이라서 아이뿐만 아니라 땅콩이를 살펴보는 용도로도 사용하고 있는데 너무 편하고 안심되더라구요!   360도 회전으로 보다 좀 더 꼼꼼하게 살펴볼 수 있고, 집이 역광으로 어둡다 싶으면 역광보정모드로 밝게도 해주더라구요! (영상참조🤍) 움직임,소리 추적 기능도 있어서 바쁘게 알려준답니다!   저희집에 곧 신생아 친구가 태어나는데 홈캠을 들여야하나 고민 많이 했는데 직접 사용해보니, 아 홈캠을 쓰는 이유가 있었구나.. 하고 느꼈답니다!  있으니까 너무 </t>
+          <t>https://www.instagram.com/p/DQ_iqr6E1tP/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>캠으로 본 감쟈 집에 혼자서도 잘 있는 착한감쟈🥔 #말티푸 #강아지 #강아지홈캠</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2011,21 +1518,31 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DW1s5OjGOg-/</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>홈캠 속 구름이 … 잔다 … 계속 잔다 …</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWinpw-EcjJ/#c18098844071479555</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>앜ㅋㅋㅋ 너무 귀엽고 웃기고 귀엽다 🤣🤣🤣</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2033,21 +1550,39 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DQ_iqr6E1tP/</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DLCoWuyyyMB/#c18074518771932808</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>캠으로 본 감쟈 집에 혼자서도 잘 있는 착한감쟈🥔 #말티푸 #강아지 #강아지홈캠</t>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>귀여워</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>안닼ㅋㅋ이건 아는 거다!!ㅋㅋㅋ너무 귀여워😆🐾🐾</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2055,21 +1590,31 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DX8kHLnk09Z/</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>🩵엄마 출근할동안 혼자 잘 놀아유 🩵 #강아지홈캠 #엄마가지켜보고있다😎</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daq4gzFEuxU/#c17932231449347501</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>마루 왜케 귀엽게 생겼닝 나랑 같은과같은뎅 🤭💕</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2077,21 +1622,31 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C6glQEWpOd2/</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2024.04.21 카메라 쳐다봤다가 거실 쳐다보는 두부🐶❤️ 오후 11시 11분인데 잠 좀 자자 근데 이날 뭐 한다고 늦게까지 집에 안 갔지? 외출할 때 주고 간 치즈바도 먹지도 않고  우리가 집 가니깐 그제서야 먹는  . . . #두부🐶#콩두부🐶 #믹스견두부❤️#강아지cctv#반려동물cctv#펫캠#홈카메라#강아지cctv녹화중 #강아지일상#반려견일상#믹스견#믹스견그램#믹스견스타그램 #밀린사진업뎃#밀린사진올리기#instadaily#bali#📷 #f4f#diy#dog🐶#애견인맞팔#애견인소통환영🙌 #두부야사랑해❤#두부야건강하고오래오래살자❤ #20240421</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ1W1uZxh_4/#c17952864606189183</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>귀요미🤍🤎🐶 콩이 ♡구름아 안뇽 반가워 제니놀러왔쏘 🐾🐾우리친구하자 💗💗💗😘🫶</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2099,21 +1654,31 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C45k2TTpmCt/</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>소꼬리사왓당 나먹을거 산것같진않은데 못마땅하게 쳐다보니 하나 푹푹 삶아서 주더랑 남의꼬리 사러 가는길도 오는길도 꼬리맛도 둑인당  #임보 #임시보호 #입양 #유기견 #유기견임보 #유기견입양 #삽살개 #삽살개믹스 #믹스견 #시고르자브종 #강아지일상 #산책 #임보일기 #강아지홈캠 #노즈워크 #사지말고입양하세요 #사지마세요입양하세요 #사지마세요입양하세요버리지마세요</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/C7Szs6YJBEa/#c18027299873293038</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>앙농 이쁘니 친구!! 소주랑 친구하자개❤️❤️</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2121,21 +1686,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DU-oAruCaYS/</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>내 뒷발차기를 받아랏..!!  밥먹구 항상 뒷발차기하는 쫑이 자신감 뿜뿜🌟  #말티푸 #강아지 #강아지일상 #강아지홈캠 #강아지뒷발차기</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZz7xG7GTBM/#c18127077421775406</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>오모오모 콩이 구름이 왜케 귀엽고 사랑스러워?!😍😘🥹</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2143,21 +1718,31 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DU-lYb5CXnq/</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>모야 모야? 움직이넹?! 옴만가?!  홈캠 의식하는 쫑이 기여워ㅓㅓ♥  #말티푸 #강아지 #강아지홈캠 #강아지일상 #말티푸그램</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DIgGRZ-TAO4/#c17955213635936196</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>홈캠 필요했었는데 요고 넘 좋네요❤️❤️</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2165,29 +1750,31 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DYrpZsoGh7Q/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>귀여워</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>뒤돌아보니까 저렇게 나만 보고 앉아있는게 귀여워서 홈캠 돌려봄 더 귀여워 … 🫠💗</t>
+          <t>https://www.instagram.com/p/C1a9l8UvWGQ/#c17849360295096145</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>펫쭈 자동급식기 넘 좋네요</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2195,21 +1782,31 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C6_WKspp4ZG/</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>달콤이 cctv 누워있는거 왜케 귀엽냐공  #강아지cctv</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd0bFwrkUQU/#c18094476260646729</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>저희 집이랑 같아요! 사용해보니 편하구 넘넘 좋더라구요!!👏</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2217,29 +1814,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C5SRWW1rMde/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>불안</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>탐이 견생일기 D+1218  견주가 분리불안이 생겨 캠을 달아 봤는데… 더 분리불안이 생김  빨리 퇴근 하고 싶다🥲  #탐이견생일기#탐스타그램#멍스타그램#강아지일상#강아지홈캠#강아지CCTV#분리불안#멍팔환영#소통해요</t>
+          <t>https://www.instagram.com/p/Da1yVwTgRd9/#c18122291068723734</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>나에게 로봇과 사는 시대란, 윤택한 삶이다</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2247,29 +1846,31 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DJ5N_GSTnT1/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>다행|불안</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>은동이는 내가 없어야 더 잘 자는 거 같다. 캠으로 보면 희한한 모양으로 잔다. 분리불안은 없어진거 같아 다행. 그러나 인간 쪽에 분리불안이 있지...  #은동이의나날 #강아지잠 #펫캠 #개스타그램 #멍스타그램 #강아지그램 #개집사 #멍집사#강아지 #반려견 #은동스타그램 #은동 #실버파티말티푸 #말티푸 #puppy #은동데이즈</t>
+          <t>https://www.instagram.com/p/Da1yVwTgRd9/#c17998101419994817</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>나에게 로봇과 사는 시대란, 든든한 베프다 ❤️😍</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2277,29 +1878,31 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CyAeihuBuB2/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>불안</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>평소에 분리불안 생길까봐  홈캠으로 절대 소리 안 내는데  뭐하고있나 봤다가 기절할뻔 ㄷ ㄷ 너무 가까워요 ,,,,</t>
+          <t>https://www.instagram.com/p/Da1yQwDAVly/#c18115325938922343</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>나에게 로봇과 사는 시대란, 든든함이다😀</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2307,21 +1910,39 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C8tqiUaJ3Qj/</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/C7Szs6YJBEa/#c18113353870344855</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>주니 임보 35일차💚  흠..내가 카메라로 훔쳐보고있는거 아는 느낌인데 이거참..  왜 당황스럽게 눈마주친거같냐..</t>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>불안</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>호빵이 분리불안 업꾸나!!!! 저도 한 분리불안 해여 .. 애기보다 더 ..</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2329,29 +1950,39 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaUGnL9pB6V/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/p/C9uLWY1zu3y/#c17866591803166235</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>불안</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>아는거마냥  그렇게 쳐다보지말라구..👀 ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ  #포인핸드 #믹스견 #똑똑이❤️ #강아지홈캠 #분리불안이뭐야</t>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>분리불안이 없어서 정말 부럽😂</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2359,29 +1990,39 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DU-EH2qkgjO/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>귀여워</t>
+          <t>https://www.instagram.com/p/Db9xwpTGXVt/#c18111703450798337</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>집에서 잘자고 있는 강쥐 훔쳐보기 모음 zip ⭐️✨🤩 #강아지홈캠 #귀여워죽음🙈❤️❤️❤️</t>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>불안</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>분리불안없어서 부러워요</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2389,21 +2030,31 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DRwUpc_EYdv/</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>왜 이러는지 모를 메리 모음.zip2 💛정💛말💛귀💛여💛워💛</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/C45k2TTpmCt/#c17990583101427800</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>백설이는 뭔가 표정이 흐뭇한 표정😍😍😍😍</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2411,21 +2062,31 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C42NxKMrEUJ/</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>처음가보는 남의집 조그만 친구에 많은 까까에 엄청난 리액션해주는 이모에 내서타일 자주와야징  #임보 #임시보호 #입양 #유기견 #유기견임보 #유기견입양 #삽살개 #삽살개믹스 #믹스견 #시고르자브종 #강아지일상 #산책 #임보일기 #강아지홈캠 #노즈워크 #사지말고입양하세요 #사지마세요입양하세요 #사지마세요입양하세요버리지마세요</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/C5FSNcPJ_GQ/#c17896934276977632</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>백설아 뭔가 잘못보냈다 나랑바꾸자😍</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>게시물</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2433,640 +2094,240 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/C5DlCKNp3tQ/</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>짠하</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>노즈워크 할줄 몰라서 수건 물고뜯는 백설이보니 정말 짠하다 어려울까봐 그냥 까까위로 수건 덮어놓기만한건데 🥺  #임보 #임시보호 #입양 #유기견 #유기견임보 #유기견입양 #삽살개 #삽살개믹스 #믹스견 #시고르자브종 #강아지일상 #산책 #임보일기 #강아지홈캠 #노즈워크 #사지말고입양하세요 #사지마세요입양하세요 #사지마세요입양하세요버리지마세요</t>
+          <t>https://www.instagram.com/p/C5aPPoLLxJl/#c18041327656742316</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>갈수록 예뻐지는 백설이🤍🤍</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>댓글</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CyisjDVRyRR/#c17973931907452282</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>악🤣🤣 사랑아❤️ 이제 곧 두발로 걷기 마스터 하겠는걸😜😝</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CyisjDVRyRR/#c18008658115989400</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>앜~~ 사랑아~ 이제까지 밤 🌃 마다 혼자 연습한거야😂😂😂😂😂</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>댓글</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CyisjDVRyRR/#c17967836717641489</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>앜ㅋㅋㅋㅋㅋㅋㅋ사랑앙 ㅋㅋㅋ이제 곧 두발로 걷는거양..?&gt;&lt; 나한테로 왕❤️</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CyisjDVRyRR/#c17973931907452282</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>악🤣🤣 사랑아❤️ 이제 곧 두발로 걷기 마스터 하겠는걸😜😝</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>댓글</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CyisjDVRyRR/#c18008658115989400</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/CyisjDVRyRR/#c17997847922500372</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>앜~~ 사랑아~ 이제까지 밤 🌃 마다 혼자 연습한거야😂😂😂😂😂</t>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>귀여워</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>헉 사랑이 짱인데 ?! 혼자 걸음마 연습하는고야 ? 귀여워💕</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>댓글</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaWgTxGJDBe/#c18560362246069111</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/C7nrEiRpAZO/</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>근뎈ㅋㅋㅋ 공포짤인데 넘 기엽네옹 ㅎㅎ❤️</t>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>걱정|안심</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>이 포스팅은 BESPOKE AI 스팀 소개 목적으로 삼성전자로부터 제품을 지원 받아 작성되었습니다.  가끔씩 반려견 시루를 집에 혼자 두고 외출할 일이 있는데, 혼자서 잘 지내는 건가 궁금하기도 하고, 걱정도 되고 하거든요?! 그런데 비스포크 AI 스팀 로봇청소기는 펫 케어 기능이 있지 뭐예요?!!!   외출을 가정하고, 스마트싱스 앱에서, 우리 집 모니터링 – 반려동물 찾기를 하면 실시간으로 비스포크 AI 스팀에 장착된 카메라로 반려견을 찾아줍니다.  너무 신기했어요! ㅎㅎㅎ 집안 곳곳을 돌아다니면서 반려견을 탐지하고 찾으면 알림 메시지도 보내준답니다. (고양이도 인식할 수 있대요!) 짖음을 감지해서 짖음 횟수도 기록해 주네요! 그리고 혼자 있는 반려견을 위해서 정서적으로 안정되고 심심하지 않게 음악과 영</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>댓글</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DIbW2KCT2BG/#c18085863652620042</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DIgGRZ-TAO4/</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>엄마가 늦게라도 올꺼라 믿구 기다리는구나 쿠크야!! 우리 쿠크 으른이네~~ !! 쿠크 정말 넘 착하고 이뻐요!!</t>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>안심</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#제품제공   아이키우는집 , 그리고 반려동물을 키우는집에 필수로 있는 홈캠 ! 저는 아이오트 홈카메라 pro 를 선택했어요.  요 귀여운 홈 카메라 친구는 베이비캠, 펫캠, 홈캠으로 최고더라구요.  저희집은 또 애만 있는 집이 아니라 애개육아를 함께 하고있는 집이라서 아이뿐만 아니라 땅콩이를 살펴보는 용도로도 사용하고 있는데 너무 편하고 안심되더라구요!   360도 회전으로 보다 좀 더 꼼꼼하게 살펴볼 수 있고, 집이 역광으로 어둡다 싶으면 역광보정모드로 밝게도 해주더라구요! (영상참조🤍) 움직임,소리 추적 기능도 있어서 바쁘게 알려준답니다!   저희집에 곧 신생아 친구가 태어나는데 홈캠을 들여야하나 고민 많이 했는데 직접 사용해보니, 아 홈캠을 쓰는 이유가 있었구나.. 하고 느꼈답니다!  있으니까 너무 </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>댓글</t>
+          <t>전체(게시물+댓글)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZz7xG7GTBM/#c18429234652125012</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>집중력보송❤️❤️ 넘 사랑스럽잖아요</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dd0bFwrkUQU/#c18009436094964744</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>저도 이제품으로 구매했는데! 화질도좋고 다 만족중이에요 😆👍🏻</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/C5FSNcPJ_GQ/#c17973212132694250</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>우와 설이 밥그릇 되게좋아보인다 🍚</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DJ1dIr6SLoW/#c18341460985089365</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>360도로 갸눙하고 너무 좋아보이는데요?😍</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Da1yVwTgRd9/#c18122291068723734</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>나에게 로봇과 사는 시대란, 윤택한 삶이다</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Da1yVwTgRd9/#c17998101419994817</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>나에게 로봇과 사는 시대란, 든든한 베프다 ❤️😍</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>3</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Da1yQwDAVly/#c18115325938922343</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>나에게 로봇과 사는 시대란, 든든함이다😀</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>4</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZFJ7v9EkmK/#c18114296077655400</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>윤서도 코비처럼 잘 잤으면 🥲</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ1UTfKk66C/#c17894374872508459</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>군밤이 정말 성격이 좋네요!!!차분히 잘 자요😍</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/C9zA-JfTUB5/#c17938317725852409</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>얌전히 잘있능 양갱이😍귀쫑긋 귀엽다</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/C9uLWY1zu3y/#c17866591803166235</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>불안</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>분리불안이 없어서 정말 부럽😂</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>5</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Db9xwpTGXVt/#c18111703450798337</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>불안</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>분리불안없어서 부러워요</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>5</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/C7Szs6YJBEa/#c18113353870344855</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>불안</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>호빵이 분리불안 업꾸나!!!! 저도 한 분리불안 해여 .. 애기보다 더 ..</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>6</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Cyk5djTJVFu/#c17985870983431213</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>기여워ㅋㅋ 현장검거 빼박이임ㅋㅋ🤪🤪🤪💛</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>6</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dc8KL7qgTI6/#c18111447737018324</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>기여워 ㅜㅜ 니모야 우리도 찌거조 🤎</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>6</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DMyc-1izlt2/#c18018968051685762</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>씨씨티비보는 봄이가 더 귀엽다🐶💛</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>7</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Cy5BDZ3LGbC/#c18018176551850384</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>밤비 혼자서도 잘있고 기특해!💛</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>7</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Cyis5g5pSS4/#c17849463087056288</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>홀리 혼자서도 잘있네 이뻐라😘😘😘</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>7</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DIbW2KCT2BG/#c18039731468238894</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>혼자서도 잘 있으니 얼마나 이뻐요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>8</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/C7Szs6YJBEa/#c18027299873293038</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>앙농 이쁘니 친구!! 소주랑 친구하자개❤️❤️</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>8</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DP52-A3D_3S/#c17896691421180127</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>너무 사랑스럽댜🥰 우리 에코랑 소나랑 친구하지않을래애~?💚</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>댓글</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>8</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ1W1uZxh_4/#c17952864606189183</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>귀요미🤍🤎🐶 콩이 ♡구름아 안뇽 반가워 제니놀러왔쏘 🐾🐾우리친구하자 💗💗💗😘🫶</t>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DR1m3H3kVyB/</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>🎉 캠봇 기능 가이드북 OPEN! – 숨겨진 꿀팁 대방출 🎉  “이 기능 뭐지?” “이거 원래 되는 거였어?”  캠봇을 쓰다 보면 한 번쯤 이런 순간 있잖아요. 이미 쓰고 계신 분들도, 이제 막 사용하시는 분들도 생각보다 모르는 기능이 꽤 많더라구요.  캠봇은 단순 홈 카메라로 보기엔 너무 아까운 제품이에요. 겉으로는 심플해 보여도, 알고 보면 훨씬 똑똑하게 쓸 수 있는 기능들이 많거든요.  그래서 준비했습니다!👩‍🏫  그동안 놓치고 지나갔던 숨은 기능부터, 알고 쓰면 하루가 편해지는 제대로 된 활용법까지!!  캠봇 기능 가이드북에서 하나씩 천천히 알려드릴게요😉  먼저 이번 첫 번째 편에서는, 캠봇 사용자라면 꼭 알고 있어야 하는 “필수 기능 BEST 5”에 대해 정리해 봤어요🎯  [💫캠봇 200% 활용 T</t>
         </is>
       </c>
     </row>
